--- a/analysis/SurveyLog_DSMB_chicago.xlsx
+++ b/analysis/SurveyLog_DSMB_chicago.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\misc_analysis\MMI\misc\DSMB Survey Updates\3D Survey\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SensorySurvey3D\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABFC783-C337-4C0E-A437-BE5E227CBC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68CA0E3-0929-4E5E-B89E-CDEF994851F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32256" yWindow="348" windowWidth="23040" windowHeight="15048" xr2:uid="{276D3F31-1118-48AD-A056-B5311D6F72EF}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{276D3F31-1118-48AD-A056-B5311D6F72EF}"/>
   </bookViews>
   <sheets>
     <sheet name="ExperimentLog" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="303">
   <si>
     <t>Subject</t>
   </si>
@@ -872,6 +872,63 @@
   </si>
   <si>
     <t>260428_1055</t>
+  </si>
+  <si>
+    <t>260429_0757</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>15 rand ch - Apr 2026</t>
+  </si>
+  <si>
+    <t>260527_0952</t>
+  </si>
+  <si>
+    <t>MEU Study - 4 groups May 2026</t>
+  </si>
+  <si>
+    <t>260528_0902</t>
+  </si>
+  <si>
+    <t>7:10,18:21</t>
+  </si>
+  <si>
+    <t>MEU Study - 8 groups May 2026</t>
+  </si>
+  <si>
+    <t>260601_1106</t>
+  </si>
+  <si>
+    <t>4:31,33</t>
+  </si>
+  <si>
+    <t>29 rand ch - June 2026</t>
+  </si>
+  <si>
+    <t>260604_0907</t>
+  </si>
+  <si>
+    <t>260604_0955</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>MEU Study - 2 groups May 2026</t>
+  </si>
+  <si>
+    <t>MEU Study - 1 group May 2026</t>
+  </si>
+  <si>
+    <t>260615_1101</t>
+  </si>
+  <si>
+    <t>5:8,12:17,24:28</t>
+  </si>
+  <si>
+    <t>MEU Study - 15 groups June 2026</t>
   </si>
 </sst>
 </file>
@@ -1367,7 +1424,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1382,17 +1439,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1802,13 +1850,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F2739B6-4284-4085-BC2B-22C994921091}">
-  <dimension ref="A1:E155"/>
+  <dimension ref="A1:E160"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.88671875" customWidth="1"/>
     <col min="3" max="3" width="55.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58" style="19" customWidth="1"/>
+    <col min="5" max="5" width="58" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1824,7 +1872,7 @@
       <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="15" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1839,22 +1887,22 @@
         <v>11</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="16" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="11">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8">
         <v>71</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="9" t="s">
         <v>35</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="16" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1869,7 +1917,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="16" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1883,7 +1931,7 @@
       <c r="C5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="16" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1897,7 +1945,7 @@
       <c r="C6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="16" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1911,7 +1959,7 @@
       <c r="C7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="16" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1925,7 +1973,7 @@
       <c r="C8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="16" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1939,7 +1987,7 @@
       <c r="C9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="16" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1953,7 +2001,7 @@
       <c r="C10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="16" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1967,7 +2015,7 @@
       <c r="C11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="16" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1981,7 +2029,7 @@
       <c r="C12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="16" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1995,7 +2043,7 @@
       <c r="C13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="16" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2009,7 +2057,7 @@
       <c r="C14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="16" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2023,49 +2071,49 @@
       <c r="C15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="16" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="11">
+      <c r="A16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="8">
         <v>269</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="16" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="11">
+      <c r="A17" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="8">
         <v>381</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="16" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="11">
+      <c r="A18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="8">
         <v>383</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="16" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2079,7 +2127,7 @@
       <c r="C19" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="16" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2093,7 +2141,7 @@
       <c r="C20" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="16" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2107,7 +2155,7 @@
       <c r="C21" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="16" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2121,21 +2169,21 @@
       <c r="C22" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="16" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="11">
+      <c r="A23" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="8">
         <v>474</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="16" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2149,7 +2197,7 @@
       <c r="C24" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="16" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2163,7 +2211,7 @@
       <c r="C25" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="16" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2178,67 +2226,67 @@
         <v>78</v>
       </c>
       <c r="D26"/>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="16" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="11">
+      <c r="A27" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="8">
         <v>583</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D27"/>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="11">
+      <c r="A28" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="8">
         <v>595</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="9" t="s">
         <v>82</v>
       </c>
       <c r="D28"/>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="11">
+      <c r="A29" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="8">
         <v>596</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="9" t="s">
         <v>84</v>
       </c>
       <c r="D29"/>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="11">
+      <c r="A30" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="8">
         <v>646</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="9" t="s">
         <v>85</v>
       </c>
       <c r="D30"/>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="16" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2253,7 +2301,7 @@
         <v>87</v>
       </c>
       <c r="D31"/>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="16" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2267,7 +2315,7 @@
       <c r="C32" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="16" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2281,35 +2329,35 @@
       <c r="C33" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="16" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="11">
+      <c r="A34" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="8">
         <v>749</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="16" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="11">
+      <c r="A35" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="8">
         <v>752</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="16" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2323,7 +2371,7 @@
       <c r="C36" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="16" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2337,7 +2385,7 @@
       <c r="C37" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="16" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2351,21 +2399,21 @@
       <c r="C38" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="16" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" s="11">
+      <c r="A39" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="8">
         <v>777</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="16" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2379,21 +2427,21 @@
       <c r="C40" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="16" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B41" s="11">
+      <c r="A41" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="8">
         <v>809</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E41" s="16" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2407,21 +2455,21 @@
       <c r="C42" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="16" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" s="11">
+      <c r="A43" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="8">
         <v>814</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E43" s="19" t="s">
+      <c r="E43" s="16" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2435,35 +2483,35 @@
       <c r="C44" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="E44" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B45" s="11">
+      <c r="A45" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="8">
         <v>835</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="E45" s="16" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B46" s="11">
+      <c r="A46" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="8">
         <v>865</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="E46" s="16" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2477,7 +2525,7 @@
       <c r="C47" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="16" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2491,185 +2539,185 @@
       <c r="C48" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="E48" s="16" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B49" s="11">
+      <c r="A49" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="8">
         <v>890</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="17" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B50" s="11">
+      <c r="A50" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="8">
         <v>891</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="17" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B51" s="11">
+      <c r="A51" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="8">
         <v>892</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="17" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B52" s="11">
+      <c r="A52" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="8">
         <v>895</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="6">
         <v>45672</v>
       </c>
-      <c r="E52" s="20" t="s">
+      <c r="E52" s="17" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B53" s="11">
+      <c r="A53" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="8">
         <v>897</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="6">
         <v>45672</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="17" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B54" s="11">
+      <c r="A54" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="8">
         <v>899</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="6">
         <v>45673</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="17" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B55" s="11">
+      <c r="A55" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="8">
         <v>912</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="6">
         <v>45714</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="17" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B56" s="11">
+      <c r="A56" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" s="8">
         <v>913</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="6">
         <v>45715</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="17" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B57" s="11">
+      <c r="A57" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="8">
         <v>914</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="6">
         <v>45715</v>
       </c>
-      <c r="E57" s="20" t="s">
+      <c r="E57" s="17" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B58" s="11">
+      <c r="A58" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="8">
         <v>915</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="6">
         <v>45715</v>
       </c>
-      <c r="E58" s="20" t="s">
+      <c r="E58" s="17" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B59" s="11">
+      <c r="A59" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="8">
         <v>925</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="6">
         <v>45737</v>
       </c>
-      <c r="E59" s="19" t="s">
+      <c r="E59" s="16" t="s">
         <v>141</v>
       </c>
     </row>
@@ -2683,401 +2731,401 @@
       <c r="C60" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="6">
         <v>45743</v>
       </c>
-      <c r="E60" s="19" t="s">
+      <c r="E60" s="16" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B61" s="11">
+      <c r="A61" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="8">
         <v>929</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="6">
         <v>45743</v>
       </c>
-      <c r="E61" s="20" t="s">
+      <c r="E61" s="17" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" s="11">
+      <c r="A62" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="8">
         <v>930</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="6">
         <v>45744</v>
       </c>
-      <c r="E62" s="20" t="s">
+      <c r="E62" s="17" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63" s="11">
+      <c r="A63" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="8">
         <v>931</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="6">
         <v>45744</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="17" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B64" s="11">
+      <c r="A64" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="8">
         <v>950</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="6">
         <v>45777</v>
       </c>
-      <c r="E64" s="20" t="s">
+      <c r="E64" s="17" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="11">
+      <c r="A65" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="8">
         <v>953</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="D65" s="10">
+      <c r="D65" s="7">
         <v>45782</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="17" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B66" s="11">
+      <c r="A66" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="8">
         <v>955</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D66" s="10">
+      <c r="D66" s="7">
         <v>45782</v>
       </c>
-      <c r="E66" s="20" t="s">
+      <c r="E66" s="17" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B67" s="11">
+      <c r="A67" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="8">
         <v>962</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D67" s="10">
+      <c r="D67" s="7">
         <v>45820</v>
       </c>
-      <c r="E67" s="20" t="s">
+      <c r="E67" s="17" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B68" s="11">
+      <c r="A68" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="8">
         <v>968</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D68" s="10">
+      <c r="D68" s="7">
         <v>45833</v>
       </c>
-      <c r="E68" s="19" t="s">
+      <c r="E68" s="16" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B69" s="11">
+      <c r="A69" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="8">
         <v>970</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="D69" s="10">
+      <c r="D69" s="7">
         <v>45840</v>
       </c>
-      <c r="E69" s="19" t="s">
+      <c r="E69" s="16" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" s="11">
+      <c r="A70" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="8">
         <v>972</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D70" s="10">
+      <c r="D70" s="7">
         <v>45841</v>
       </c>
-      <c r="E70" s="19" t="s">
+      <c r="E70" s="16" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" s="11">
+      <c r="A71" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="8">
         <v>975</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D71" s="10">
+      <c r="D71" s="7">
         <v>45862</v>
       </c>
-      <c r="E71" s="19" t="s">
+      <c r="E71" s="16" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" s="11">
+      <c r="A72" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="8">
         <v>976</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D72" s="10">
+      <c r="D72" s="7">
         <v>45862</v>
       </c>
-      <c r="E72" s="19" t="s">
+      <c r="E72" s="16" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B73" s="11">
+      <c r="A73" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="8">
         <v>978</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D73" s="10">
+      <c r="D73" s="7">
         <v>45868</v>
       </c>
-      <c r="E73" s="19" t="s">
+      <c r="E73" s="16" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B74" s="11">
+      <c r="A74" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="8">
         <v>979</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="D74" s="10">
+      <c r="D74" s="7">
         <v>45876</v>
       </c>
-      <c r="E74" s="20" t="s">
+      <c r="E74" s="17" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="11">
+      <c r="A75" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="8">
         <v>986</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="D75" s="10">
+      <c r="D75" s="7">
         <v>45877</v>
       </c>
-      <c r="E75" s="20" t="s">
+      <c r="E75" s="17" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B76" s="11">
+      <c r="A76" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="8">
         <v>988</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D76" s="10">
+      <c r="D76" s="7">
         <v>45877</v>
       </c>
-      <c r="E76" s="20" t="s">
+      <c r="E76" s="17" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B77" s="11">
+      <c r="A77" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="8">
         <v>1000</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D77" s="10">
+      <c r="D77" s="7">
         <v>45936</v>
       </c>
-      <c r="E77" s="19" t="s">
+      <c r="E77" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B78" s="11">
+      <c r="A78" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="8">
         <v>1001</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D78" s="10">
+      <c r="D78" s="7">
         <v>45947</v>
       </c>
-      <c r="E78" s="19" t="s">
+      <c r="E78" s="16" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B79" s="11">
+      <c r="A79" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="8">
         <v>1003</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D79" s="10">
+      <c r="D79" s="7">
         <v>45954</v>
       </c>
-      <c r="E79" s="20" t="s">
+      <c r="E79" s="17" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B80" s="11">
+      <c r="A80" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="8">
         <v>1004</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="D80" s="10">
+      <c r="D80" s="7">
         <v>45954</v>
       </c>
-      <c r="E80" s="20" t="s">
+      <c r="E80" s="17" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B81" s="11">
+      <c r="A81" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="8">
         <v>1005</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="9" t="s">
         <v>154</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E81" s="20" t="s">
+      <c r="E81" s="17" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B82" s="11">
+      <c r="A82" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="8">
         <v>1007</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D82" s="10">
+      <c r="D82" s="7">
         <v>45967</v>
       </c>
-      <c r="E82" s="19" t="s">
+      <c r="E82" s="16" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B83" s="11">
+      <c r="A83" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="8">
         <v>1009</v>
       </c>
-      <c r="C83" s="12" t="s">
+      <c r="C83" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D83" s="13">
+      <c r="D83" s="10">
         <v>45973</v>
       </c>
-      <c r="E83" s="19" t="s">
+      <c r="E83" s="16" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3086,471 +3134,485 @@
       <c r="D84"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B85" s="11" t="s">
+      <c r="A85" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D85" s="13">
+      <c r="D85" s="10">
         <v>46001</v>
       </c>
-      <c r="E85" s="19" t="s">
+      <c r="E85" s="16" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B86" s="11" t="s">
+      <c r="A86" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D86" s="13">
+      <c r="D86" s="10">
         <v>46009</v>
       </c>
-      <c r="E86" s="20" t="s">
+      <c r="E86" s="17" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B87" s="11" t="s">
+      <c r="A87" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="D87" s="13">
+      <c r="D87" s="10">
         <v>46010</v>
       </c>
-      <c r="E87" s="20" t="s">
+      <c r="E87" s="17" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B88" s="11" t="s">
+      <c r="A88" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="C88" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="D88" s="13">
+      <c r="D88" s="10">
         <v>46014</v>
       </c>
-      <c r="E88" s="20" t="s">
+      <c r="E88" s="17" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B89" s="17" t="s">
+      <c r="A89" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C89" s="17" t="s">
+      <c r="C89" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="D89" s="13">
+      <c r="D89" s="10">
         <v>46030</v>
       </c>
-      <c r="E89" s="19" t="s">
+      <c r="E89" s="16" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B90" s="11" t="s">
+      <c r="A90" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="D90" s="13">
+      <c r="D90" s="10">
         <v>46044</v>
       </c>
-      <c r="E90" s="19" t="s">
+      <c r="E90" s="16" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B91" s="11" t="s">
+      <c r="A91" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="C91" s="12" t="s">
+      <c r="C91" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="D91" s="13">
+      <c r="D91" s="10">
         <v>46085</v>
       </c>
-      <c r="E91" s="20" t="s">
+      <c r="E91" s="17" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B92" s="11" t="s">
+      <c r="A92" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="D92" s="13">
+      <c r="D92" s="10">
         <v>46086</v>
       </c>
-      <c r="E92" s="20" t="s">
+      <c r="E92" s="17" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B93" s="11" t="s">
+      <c r="A93" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="C93" s="12" t="s">
+      <c r="C93" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="D93" s="13">
+      <c r="D93" s="10">
         <v>46087</v>
       </c>
-      <c r="E93" s="19" t="s">
+      <c r="E93" s="17" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B94" s="17" t="s">
+      <c r="A94" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="C94" s="17" t="s">
+      <c r="C94" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="D94" s="13">
+      <c r="D94" s="10">
         <v>46092</v>
       </c>
-      <c r="E94" s="21" t="s">
+      <c r="E94" s="18" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B95" s="17" t="s">
+      <c r="A95" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="C95" s="17" t="s">
+      <c r="C95" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="D95" s="13">
+      <c r="D95" s="10">
         <v>46093</v>
       </c>
-      <c r="E95" s="21" t="s">
+      <c r="E95" s="18" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C96" s="5"/>
-      <c r="D96"/>
+      <c r="A96" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="D96" s="10">
+        <v>46141</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B97" s="11">
+      <c r="A97" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="10">
+        <v>46169</v>
+      </c>
+      <c r="E97" s="19" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="D98" s="10">
+        <v>46170</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D99" s="10">
+        <v>46177</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="D100" s="10">
+        <v>46177</v>
+      </c>
+      <c r="E100" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C101" s="5"/>
+      <c r="D101"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B102" s="8">
         <v>56</v>
       </c>
-      <c r="C97" s="12" t="s">
+      <c r="C102" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="D97"/>
-      <c r="E97" s="19" t="s">
+      <c r="D102"/>
+      <c r="E102" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B98" s="11">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B103" s="8">
         <v>64</v>
       </c>
-      <c r="C98" s="12" t="s">
+      <c r="C103" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E98" s="19" t="s">
+      <c r="E103" s="16" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B99" s="11">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B104" s="8">
         <v>76</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C104" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="D99" s="8"/>
-      <c r="E99" s="19" t="s">
+      <c r="D104" s="6"/>
+      <c r="E104" s="16" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B100" s="11">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B105" s="8">
         <v>98</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C105" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D100" s="8"/>
-      <c r="E100" s="19" t="s">
+      <c r="D105" s="6"/>
+      <c r="E105" s="16" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B101" s="11">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B106" s="8">
         <v>99</v>
       </c>
-      <c r="C101" s="12" t="s">
+      <c r="C106" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D101" s="8"/>
-      <c r="E101" s="19" t="s">
+      <c r="D106" s="6"/>
+      <c r="E106" s="16" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B102" s="11">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B107" s="8">
         <v>100</v>
       </c>
-      <c r="C102" s="12" t="s">
+      <c r="C107" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E102" s="19" t="s">
+      <c r="E107" s="16" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B103" s="11">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B108" s="8">
         <v>101</v>
       </c>
-      <c r="C103" s="12" t="s">
+      <c r="C108" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E103" s="19" t="s">
+      <c r="E108" s="16" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B104" s="11">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B109" s="8">
         <v>104</v>
       </c>
-      <c r="C104" s="12" t="s">
+      <c r="C109" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="E104" s="19" t="s">
+      <c r="E109" s="16" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B105" s="11">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B110" s="8">
         <v>105</v>
       </c>
-      <c r="C105" s="12" t="s">
+      <c r="C110" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="D105"/>
-      <c r="E105" s="19" t="s">
+      <c r="D110"/>
+      <c r="E110" s="16" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B106" s="11">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B111" s="8">
         <v>106</v>
       </c>
-      <c r="C106" s="12" t="s">
+      <c r="C111" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="D106"/>
-      <c r="E106" s="19" t="s">
+      <c r="D111"/>
+      <c r="E111" s="16" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B107" s="11">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B112" s="8">
         <v>107</v>
       </c>
-      <c r="C107" s="12" t="s">
+      <c r="C112" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="D107"/>
-      <c r="E107" s="19" t="s">
+      <c r="D112"/>
+      <c r="E112" s="16" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B108" s="11">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B113" s="8">
         <v>108</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="C113" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="D108"/>
-      <c r="E108" s="19" t="s">
+      <c r="D113"/>
+      <c r="E113" s="16" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B109" s="11">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B114" s="8">
         <v>113</v>
       </c>
-      <c r="C109" s="12" t="s">
+      <c r="C114" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D109" s="8"/>
-      <c r="E109" s="19" t="s">
+      <c r="D114" s="6"/>
+      <c r="E114" s="16" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B110" s="11">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B115" s="8">
         <v>114</v>
       </c>
-      <c r="C110" s="12" t="s">
+      <c r="C115" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="D110" s="8"/>
-      <c r="E110" s="19" t="s">
+      <c r="D115" s="6"/>
+      <c r="E115" s="16" t="s">
         <v>210</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>4</v>
-      </c>
-      <c r="B111">
-        <v>115</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D111" s="10"/>
-      <c r="E111" s="19" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B112" s="11">
-        <v>117</v>
-      </c>
-      <c r="C112" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="E112" s="19" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B113" s="11">
-        <v>118</v>
-      </c>
-      <c r="C113" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="E113" s="19" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>4</v>
-      </c>
-      <c r="B114">
-        <v>122</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E114" s="19" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>4</v>
-      </c>
-      <c r="B115">
-        <v>123</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="E115" s="19" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -3558,83 +3620,84 @@
         <v>4</v>
       </c>
       <c r="B116">
+        <v>115</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D116" s="7"/>
+      <c r="E116" s="16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B117" s="8">
+        <v>117</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E117" s="16" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B118" s="8">
+        <v>118</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E118" s="16" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>4</v>
+      </c>
+      <c r="B119">
+        <v>122</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E119" s="16" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>4</v>
+      </c>
+      <c r="B120">
+        <v>123</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E120" s="16" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>4</v>
+      </c>
+      <c r="B121">
         <v>124</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="C121" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E116" s="19" t="s">
+      <c r="E121" s="16" t="s">
         <v>214</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>4</v>
-      </c>
-      <c r="B117">
-        <v>129</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="E117" s="19" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B118" s="11">
-        <v>135</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E118" s="19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B119" s="11">
-        <v>136</v>
-      </c>
-      <c r="C119" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="E119" s="19" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B120" s="11">
-        <v>150</v>
-      </c>
-      <c r="C120" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="E120" s="19" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B121" s="11">
-        <v>151</v>
-      </c>
-      <c r="C121" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E121" s="19" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -3642,89 +3705,83 @@
         <v>4</v>
       </c>
       <c r="B122">
+        <v>129</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="E122" s="16" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B123" s="8">
+        <v>135</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E123" s="16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B124" s="8">
+        <v>136</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E124" s="16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B125" s="8">
+        <v>150</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E125" s="16" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B126" s="8">
+        <v>151</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E126" s="16" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>4</v>
+      </c>
+      <c r="B127">
         <v>179</v>
       </c>
-      <c r="C122" s="5" t="s">
+      <c r="C127" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E122" s="19" t="s">
+      <c r="E127" s="16" t="s">
         <v>219</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>4</v>
-      </c>
-      <c r="B123">
-        <v>206</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="E123" s="19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>4</v>
-      </c>
-      <c r="B124">
-        <v>208</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E124" s="19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>4</v>
-      </c>
-      <c r="B125">
-        <v>210</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E125" s="19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B126" s="11">
-        <v>219</v>
-      </c>
-      <c r="C126" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D126" s="8">
-        <v>45706</v>
-      </c>
-      <c r="E126" s="20" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B127" s="11">
-        <v>224</v>
-      </c>
-      <c r="C127" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D127" s="8">
-        <v>45734</v>
-      </c>
-      <c r="E127" s="20" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -3732,345 +3789,441 @@
         <v>4</v>
       </c>
       <c r="B128">
+        <v>206</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E128" s="16" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>4</v>
+      </c>
+      <c r="B129">
+        <v>208</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E129" s="16" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>4</v>
+      </c>
+      <c r="B130">
+        <v>210</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E130" s="16" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B131" s="8">
+        <v>219</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D131" s="6">
+        <v>45706</v>
+      </c>
+      <c r="E131" s="17" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B132" s="8">
+        <v>224</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D132" s="6">
+        <v>45734</v>
+      </c>
+      <c r="E132" s="17" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>4</v>
+      </c>
+      <c r="B133">
         <v>225</v>
       </c>
-      <c r="C128" s="5" t="s">
+      <c r="C133" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D128" s="8">
+      <c r="D133" s="6">
         <v>45735</v>
       </c>
-      <c r="E128" s="19" t="s">
+      <c r="E133" s="16" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B129" s="11">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B134" s="8">
         <v>244</v>
       </c>
-      <c r="C129" s="12" t="s">
+      <c r="C134" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D129" s="8">
+      <c r="D134" s="6">
         <v>45775</v>
       </c>
-      <c r="E129" s="20" t="s">
+      <c r="E134" s="17" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B130" s="11">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B135" s="8">
         <v>252</v>
       </c>
-      <c r="C130" s="12" t="s">
+      <c r="C135" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="D130" s="8">
+      <c r="D135" s="6">
         <v>45805</v>
       </c>
-      <c r="E130" s="20" t="s">
+      <c r="E135" s="17" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B131" s="11">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B136" s="8">
         <v>255</v>
       </c>
-      <c r="C131" s="12" t="s">
+      <c r="C136" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="D131" s="10">
+      <c r="D136" s="7">
         <v>45818</v>
       </c>
-      <c r="E131" s="19" t="s">
+      <c r="E136" s="16" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B132" s="11">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B137" s="8">
         <v>258</v>
       </c>
-      <c r="C132" s="12" t="s">
+      <c r="C137" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D132" s="10">
+      <c r="D137" s="7">
         <v>45852</v>
       </c>
-      <c r="E132" s="20" t="s">
+      <c r="E137" s="17" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B133" s="11">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B138" s="8">
         <v>267</v>
       </c>
-      <c r="C133" s="12" t="s">
+      <c r="C138" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="D133" s="10">
+      <c r="D138" s="7">
         <v>45903</v>
       </c>
-      <c r="E133" s="19" t="s">
+      <c r="E138" s="16" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B134" s="11">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B139" s="8">
         <v>269</v>
       </c>
-      <c r="C134" s="12" t="s">
+      <c r="C139" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D134" s="10">
+      <c r="D139" s="7">
         <v>45909</v>
       </c>
-      <c r="E134" s="19" t="s">
+      <c r="E139" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B135" s="11">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B140" s="8">
         <v>277</v>
       </c>
-      <c r="C135" s="12" t="s">
+      <c r="C140" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D135" s="10">
+      <c r="D140" s="7">
         <v>45923</v>
       </c>
-      <c r="E135" s="19" t="s">
+      <c r="E140" s="16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B136" s="11">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B141" s="8">
         <v>278</v>
       </c>
-      <c r="C136" s="12" t="s">
+      <c r="C141" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="D136" s="10">
+      <c r="D141" s="7">
         <v>45924</v>
       </c>
-      <c r="E136" s="20" t="s">
+      <c r="E141" s="17" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C137" s="5"/>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B138" s="11" t="s">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C142" s="5"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B143" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C138" s="12" t="s">
+      <c r="C143" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="D138" s="10">
+      <c r="D143" s="7">
         <v>45966</v>
       </c>
-      <c r="E138" s="19" t="s">
+      <c r="E143" s="16" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B139" s="11" t="s">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B144" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C139" s="15" t="s">
+      <c r="C144" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D139" s="10">
+      <c r="D144" s="7">
         <v>45999</v>
       </c>
-      <c r="E139" s="19" t="s">
+      <c r="E144" s="16" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B140" s="11" t="s">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B145" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C140" s="14" t="s">
+      <c r="C145" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D140" s="10">
+      <c r="D145" s="7">
         <v>46000</v>
       </c>
-      <c r="E140" s="20" t="s">
+      <c r="E145" s="17" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B141" s="11" t="s">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B146" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C141" s="12" t="s">
+      <c r="C146" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="D141" s="10">
+      <c r="D146" s="7">
         <v>46077</v>
       </c>
-      <c r="E141" s="20" t="s">
+      <c r="E146" s="17" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B142" s="16" t="s">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B147" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="C142" s="17" t="s">
+      <c r="C147" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="D142" s="10">
+      <c r="D147" s="7">
         <v>46078</v>
       </c>
-      <c r="E142" s="20" t="s">
+      <c r="E147" s="17" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A143" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B143" s="17" t="s">
+    <row r="148" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A148" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B148" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="C143" s="17" t="s">
+      <c r="C148" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="D143" s="8">
+      <c r="D148" s="6">
         <v>46085</v>
       </c>
-      <c r="E143" s="21" t="s">
+      <c r="E148" s="18" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B144" s="17" t="s">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B149" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="C144" s="17" t="s">
+      <c r="C149" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="D144" s="8">
+      <c r="D149" s="6">
         <v>46105</v>
       </c>
-      <c r="E144" s="21" t="s">
+      <c r="E149" s="18" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B145" s="17" t="s">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B150" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="C145" s="17" t="s">
+      <c r="C150" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="D145" s="8">
+      <c r="D150" s="6">
         <v>46139</v>
       </c>
-      <c r="E145" s="22" t="s">
+      <c r="E150" s="19" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B146" s="17" t="s">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B151" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="C146" s="17" t="s">
+      <c r="C151" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="D146" s="8">
+      <c r="D151" s="6">
         <v>46140</v>
       </c>
-      <c r="E146" s="22" t="s">
+      <c r="E151" s="19" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A147" s="6"/>
-      <c r="B147" s="7"/>
-      <c r="C147" s="9"/>
-      <c r="D147" s="8"/>
-      <c r="E147" s="21"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" s="6"/>
-      <c r="B148" s="7"/>
-      <c r="C148" s="9"/>
-      <c r="D148" s="8"/>
-      <c r="E148" s="21"/>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D149" s="10"/>
-      <c r="E149" s="21"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C150" s="5"/>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C151" s="5"/>
-    </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C152" s="5"/>
+      <c r="A152" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B152" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="D152" s="6">
+        <v>46174</v>
+      </c>
+      <c r="E152" s="18" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C153" s="5"/>
+      <c r="A153" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B153" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="D153" s="6">
+        <v>46188</v>
+      </c>
+      <c r="E153" s="19" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C154" s="5"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="18"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C155" s="5"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C156" s="5"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C157" s="5"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C158" s="5"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C159" s="5"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C160" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
